--- a/luban-excels/bak2/xlsx/__enums__.xlsx
+++ b/luban-excels/bak2/xlsx/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="251">
   <si>
     <t>##var</t>
   </si>
@@ -116,9 +116,6 @@
     <t>手臂层的装饰</t>
   </si>
   <si>
-    <t>例如纹身</t>
-  </si>
-  <si>
     <t>Clothes</t>
   </si>
   <si>
@@ -164,34 +161,55 @@
     <t>卡面</t>
   </si>
   <si>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
+    <t>体表装饰</t>
+  </si>
+  <si>
+    <t>玩家身体装饰（体毛、纹身、美甲等）</t>
+  </si>
+  <si>
     <t>ERarity</t>
   </si>
   <si>
     <t>物品稀有度</t>
   </si>
   <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>优秀</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
     <t>Legendary</t>
   </si>
   <si>
     <t>传说</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>普通</t>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>神话</t>
   </si>
   <si>
     <t>Special1</t>
@@ -392,6 +410,12 @@
     <t>拒绝</t>
   </si>
   <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>哈喽</t>
+  </si>
+  <si>
     <t>WaitingForBet</t>
   </si>
   <si>
@@ -443,16 +467,22 @@
     <t>看到结算结果</t>
   </si>
   <si>
+    <t>InteractionHint</t>
+  </si>
+  <si>
+    <t>提示玩家可以询问</t>
+  </si>
+  <si>
     <t>SawNothing</t>
   </si>
   <si>
     <t>看到坏牌</t>
   </si>
   <si>
-    <t>SawJacksOrBetter</t>
-  </si>
-  <si>
-    <t>看到高对</t>
+    <t>SawOnePair</t>
+  </si>
+  <si>
+    <t>看到一对</t>
   </si>
   <si>
     <t>SawTwoPair</t>
@@ -515,10 +545,10 @@
     <t>坏牌</t>
   </si>
   <si>
-    <t>JacksOrBetter</t>
-  </si>
-  <si>
-    <t>高对</t>
+    <t>OnePair</t>
+  </si>
+  <si>
+    <t>一对</t>
   </si>
   <si>
     <t>TwoPair</t>
@@ -677,16 +707,79 @@
     <t>这个显式枚举值可能会变，到时候会改成Steam要求的枚举值，因此使用时不要根据int值来判断</t>
   </si>
   <si>
-    <t>EEnumType</t>
-  </si>
-  <si>
-    <t>枚举类型</t>
-  </si>
-  <si>
-    <t>EDogAction</t>
-  </si>
-  <si>
-    <t>GameState</t>
+    <t/>
+  </si>
+  <si>
+    <t>EAchievementRuleType</t>
+  </si>
+  <si>
+    <t>成就判定规则</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType</t>
+  </si>
+  <si>
+    <t>首次获得非初始道具部位</t>
+  </si>
+  <si>
+    <t>FirstExternalItemRarity</t>
+  </si>
+  <si>
+    <t>首次获得非初始指定品质道具</t>
+  </si>
+  <si>
+    <t>FirstEvent</t>
+  </si>
+  <si>
+    <t>首次发生游戏事件</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast</t>
+  </si>
+  <si>
+    <t>玩家统计达到数值</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticUnit</t>
+  </si>
+  <si>
+    <t>玩家统计单位</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>次数</t>
+  </si>
+  <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>筹码</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>秒</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticType</t>
+  </si>
+  <si>
+    <t>玩家统计类型</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>只增累计</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>最高记录</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1769,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -1864,9 +1957,7 @@
       <c r="J7" s="5">
         <v>4</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="K7" s="5"/>
       <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12">
@@ -1878,10 +1969,10 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="J8" s="5">
         <v>5</v>
@@ -1898,10 +1989,10 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="J9" s="5">
         <v>6</v>
@@ -1918,10 +2009,10 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="J10" s="5">
         <v>7</v>
@@ -1938,10 +2029,10 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="J11" s="5">
         <v>8</v>
@@ -1958,16 +2049,16 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="J12" s="5">
         <v>9</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L12" s="5"/>
     </row>
@@ -1980,10 +2071,10 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="J13" s="5">
         <v>10</v>
@@ -2000,10 +2091,10 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="J14" s="5">
         <v>11</v>
@@ -2012,29 +2103,40 @@
       <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="5" t="b">
+      <c r="J15" s="5">
+        <v>12</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="D16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
       <c r="H16" s="1" t="s">
         <v>49</v>
       </c>
@@ -2042,11 +2144,10 @@
         <v>50</v>
       </c>
       <c r="J16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" ht="18" spans="1:11">
-      <c r="A17" s="6"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="H17" s="1" t="s">
         <v>51</v>
       </c>
@@ -2054,10 +2155,11 @@
         <v>52</v>
       </c>
       <c r="J17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:11">
+      <c r="A18" s="6"/>
       <c r="H18" s="1" t="s">
         <v>53</v>
       </c>
@@ -2076,294 +2178,294 @@
         <v>56</v>
       </c>
       <c r="J19" s="1">
-        <v>5</v>
-      </c>
-      <c r="K19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="H20" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="H21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="1">
-        <v>6</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="B21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:11">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="H22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="1">
+        <v>21</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="H23" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="H22" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J23" s="1">
+        <v>22</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="1">
+      <c r="C24" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="H25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="1">
         <v>2</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="H23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" s="1">
-        <v>4</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="H24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J24" s="1">
-        <v>8</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="H25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J25" s="1">
-        <v>16</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="H26" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J26" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="H27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="1">
+        <v>8</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="H28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="1">
-        <v>64</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="J28" s="1">
+        <v>16</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="H28" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J28" s="1">
-        <v>128</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="H29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="1">
+        <v>32</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="H30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="1">
-        <v>256</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="J30" s="1">
+        <v>64</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="H30" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J30" s="1">
-        <v>512</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="H31" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J31" s="1">
-        <v>1024</v>
+        <v>128</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="H32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J32" s="1">
+        <v>256</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="H33" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I33" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J32" s="1">
-        <v>2048</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="J33" s="1">
+        <v>512</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:11">
       <c r="H34" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J34" s="1">
-        <v>2</v>
+        <v>1024</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2048</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="C36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J35" s="1">
-        <v>1001</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="H36" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="J36" s="1">
-        <v>1002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="H37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1003</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="H38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1">
+        <v>1001</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J38" s="1">
-        <v>1004</v>
-      </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
       <c r="H39" s="1" t="s">
         <v>113</v>
       </c>
@@ -2371,7 +2473,7 @@
         <v>114</v>
       </c>
       <c r="J39" s="1">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2382,7 +2484,7 @@
         <v>116</v>
       </c>
       <c r="J40" s="1">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2393,10 +2495,12 @@
         <v>118</v>
       </c>
       <c r="J41" s="1">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="42" spans="2:11">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
       <c r="H42" s="1" t="s">
         <v>119</v>
       </c>
@@ -2404,40 +2508,40 @@
         <v>120</v>
       </c>
       <c r="J42" s="1">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="H43" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="H44" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="H45" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="1">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="H43" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J43" s="5">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="H44" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J44" s="5">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="H45" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J45" s="5">
-        <v>2003</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2447,113 +2551,116 @@
       <c r="I46" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="1">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="H47" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="5">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="H48" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J48" s="5">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="49" spans="8:11">
+      <c r="H49" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J49" s="5">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="50" spans="8:11">
+      <c r="H50" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="5">
         <v>2004</v>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="H47" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J47" s="5">
+    <row r="51" spans="8:11">
+      <c r="H51" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J51" s="5">
         <v>2005</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="H48" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J48" s="5">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="49" spans="8:10">
-      <c r="H49" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J49" s="5">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="50" spans="8:10">
-      <c r="H50" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="J50" s="5">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="51" spans="8:10">
-      <c r="H51" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I51" s="1" t="s">
+      <c r="K51" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J51" s="1">
-        <v>3001</v>
-      </c>
-    </row>
-    <row r="52" spans="8:10">
+    </row>
+    <row r="52" spans="8:11">
       <c r="H52" s="1" t="s">
         <v>140</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J52" s="1">
-        <v>3002</v>
-      </c>
-    </row>
-    <row r="53" spans="8:10">
-      <c r="H53" s="1" t="s">
+      <c r="J52" s="5">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="53" spans="8:11">
+      <c r="H53" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="J53" s="1">
-        <v>3003</v>
-      </c>
-    </row>
-    <row r="54" spans="8:10">
-      <c r="H54" s="1" t="s">
+      <c r="J53" s="5">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="54" spans="8:11">
+      <c r="H54" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="J54" s="1">
-        <v>3004</v>
-      </c>
-    </row>
-    <row r="55" spans="8:10">
-      <c r="H55" s="1" t="s">
+      <c r="J54" s="5">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="55" spans="8:11">
+      <c r="H55" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="J55" s="1">
-        <v>3005</v>
-      </c>
-    </row>
-    <row r="56" spans="8:10">
+      <c r="J55" s="5">
+        <v>2009</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="8:11">
       <c r="H56" s="1" t="s">
         <v>148</v>
       </c>
@@ -2561,10 +2668,10 @@
         <v>149</v>
       </c>
       <c r="J56" s="1">
-        <v>3006</v>
-      </c>
-    </row>
-    <row r="57" spans="8:10">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="57" spans="8:11">
       <c r="H57" s="1" t="s">
         <v>150</v>
       </c>
@@ -2572,10 +2679,10 @@
         <v>151</v>
       </c>
       <c r="J57" s="1">
-        <v>3007</v>
-      </c>
-    </row>
-    <row r="58" spans="8:10">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="58" spans="8:11">
       <c r="H58" s="1" t="s">
         <v>152</v>
       </c>
@@ -2583,10 +2690,10 @@
         <v>153</v>
       </c>
       <c r="J58" s="1">
-        <v>3008</v>
-      </c>
-    </row>
-    <row r="59" spans="8:10">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="59" spans="8:11">
       <c r="H59" s="1" t="s">
         <v>154</v>
       </c>
@@ -2594,10 +2701,10 @@
         <v>155</v>
       </c>
       <c r="J59" s="1">
-        <v>3009</v>
-      </c>
-    </row>
-    <row r="60" spans="8:10">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="60" spans="8:11">
       <c r="H60" s="1" t="s">
         <v>156</v>
       </c>
@@ -2605,79 +2712,77 @@
         <v>157</v>
       </c>
       <c r="J60" s="1">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="61" spans="8:11">
+      <c r="H61" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J61" s="1">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="62" spans="8:11">
+      <c r="H62" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J62" s="1">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="63" spans="8:11">
+      <c r="H63" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J63" s="1">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="64" spans="8:11">
+      <c r="H64" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J64" s="1">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
+      <c r="H65" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J65" s="1">
         <v>3010</v>
       </c>
     </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="5" t="b">
+    <row r="70" spans="2:10">
+      <c r="B70" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D65" s="5" t="b">
+      <c r="D70" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="H66" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J66" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="H67" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J67" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="H68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J68" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="H69" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I69" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
       <c r="H70" s="1" t="s">
         <v>170</v>
       </c>
@@ -2685,10 +2790,10 @@
         <v>171</v>
       </c>
       <c r="J70" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
       <c r="H71" s="1" t="s">
         <v>172</v>
       </c>
@@ -2696,10 +2801,10 @@
         <v>173</v>
       </c>
       <c r="J71" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
       <c r="H72" s="1" t="s">
         <v>174</v>
       </c>
@@ -2707,10 +2812,10 @@
         <v>175</v>
       </c>
       <c r="J72" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10">
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="H73" s="1" t="s">
@@ -2720,10 +2825,10 @@
         <v>177</v>
       </c>
       <c r="J73" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
       <c r="H74" s="1" t="s">
         <v>178</v>
       </c>
@@ -2731,258 +2836,607 @@
         <v>179</v>
       </c>
       <c r="J74" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
+      <c r="H75" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J75" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
+      <c r="H76" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J76" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
+      <c r="H77" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J77" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="H78" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J78" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
+      <c r="H79" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J79" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C75" s="5" t="b">
+    <row r="80" spans="2:10">
+      <c r="B80" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C80" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D75" s="5" t="b">
+      <c r="D80" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="J75" s="1">
+      <c r="F80" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J80" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:11">
-      <c r="H76" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J76" s="1">
+    <row r="81" spans="1:12">
+      <c r="H81" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J81" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:11">
-      <c r="H77" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J77" s="1">
+    <row r="82" spans="1:12">
+      <c r="H82" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J82" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="2:11">
-      <c r="H78" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J78" s="1">
+    <row r="83" spans="1:12">
+      <c r="H83" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J83" s="1">
         <v>4</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="H79" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J79" s="1">
+      <c r="K83" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="H84" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J84" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="2:11">
-      <c r="H80" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J80" s="1">
+    <row r="85" spans="1:12">
+      <c r="H85" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J85" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C81" s="5" t="b">
+    <row r="86" spans="1:12">
+      <c r="B86" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D81" s="5" t="b">
+      <c r="D86" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J81" s="1">
+      <c r="F86" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J86" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:11">
-      <c r="H82" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J82" s="1">
+    <row r="87" spans="1:12">
+      <c r="H87" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J87" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:11">
-      <c r="H83" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J83" s="1">
+    <row r="88" spans="1:12">
+      <c r="H88" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J88" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="2:11">
-      <c r="H84" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="J84" s="1">
+    <row r="89" spans="1:12">
+      <c r="H89" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J89" s="1">
         <v>4</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C85" s="5" t="b">
+      <c r="K89" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D85" s="5" t="b">
+      <c r="D90" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J85" s="1">
+      <c r="F90" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J90" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:11">
-      <c r="H86" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J86" s="1">
+    <row r="91" spans="1:12">
+      <c r="H91" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J91" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C87" s="5" t="b">
+    <row r="92" spans="1:12">
+      <c r="B92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D87" s="5" t="b">
+      <c r="D92" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J87" s="1">
+      <c r="F92" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J92" s="1">
         <v>1</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9">
+      <c r="K92" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J96" s="1">
+        <v>2</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J97" s="1">
+        <v>3</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J98" s="1">
+        <v>4</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C99" s="5" t="b">
+        <v>237</v>
+      </c>
+      <c r="C99" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D99" s="5" t="b">
+      <c r="D99" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E99" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="F99" s="1" t="s">
-        <v>217</v>
+        <v>238</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9">
+        <v>239</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="H100" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9">
+        <v>241</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="H101" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9">
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="I112" s="5"/>
-    </row>
-    <row r="113" spans="3:9">
-      <c r="I113" s="5"/>
-    </row>
-    <row r="114" spans="3:9">
-      <c r="I114" s="5"/>
-    </row>
-    <row r="115" spans="3:9">
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-    </row>
-    <row r="116" spans="3:9">
-      <c r="I116" s="5"/>
-    </row>
-    <row r="118" spans="3:9">
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
-      <c r="I118" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J101" s="1">
+        <v>3</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J103" s="1">
+        <v>2</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/luban-excels/bak2/xlsx/__enums__.xlsx
+++ b/luban-excels/bak2/xlsx/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="295">
   <si>
     <t>##var</t>
   </si>
@@ -692,94 +692,226 @@
     <t>直接展示奖励</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>EAchievementRuleType</t>
+  </si>
+  <si>
+    <t>成就判定规则</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType</t>
+  </si>
+  <si>
+    <t>首次获得非初始道具部位</t>
+  </si>
+  <si>
+    <t>FirstExternalItemRarity</t>
+  </si>
+  <si>
+    <t>首次获得非初始指定品质道具</t>
+  </si>
+  <si>
+    <t>FirstEvent</t>
+  </si>
+  <si>
+    <t>首次发生游戏事件</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast</t>
+  </si>
+  <si>
+    <t>玩家统计达到数值</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticUnit</t>
+  </si>
+  <si>
+    <t>玩家统计单位</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>次数</t>
+  </si>
+  <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>筹码</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>秒</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticType</t>
+  </si>
+  <si>
+    <t>玩家统计类型</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>只增累计</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>最高记录</t>
+  </si>
+  <si>
+    <t>ELinkTreeOpenCheckType</t>
+  </si>
+  <si>
+    <t>LinkTree 外部链接打开后的客户端侧校验方式</t>
+  </si>
+  <si>
+    <t>不校验</t>
+  </si>
+  <si>
+    <t>不做打开校验；通常只用于纯展示入口</t>
+  </si>
+  <si>
+    <t>ShellOpenOk</t>
+  </si>
+  <si>
+    <t>ShellOpen 成功</t>
+  </si>
+  <si>
+    <t>OS.ShellOpen 返回 Error.Ok 后允许进入可领取状态</t>
+  </si>
+  <si>
+    <t>SteamClientOk</t>
+  </si>
+  <si>
+    <t>Steam 客户端成功</t>
+  </si>
+  <si>
+    <t>预留：确认 Steam 客户端或 Steam overlay 成功打开后允许领取</t>
+  </si>
+  <si>
+    <t>BrowserProcessOk</t>
+  </si>
+  <si>
+    <t>浏览器进程成功</t>
+  </si>
+  <si>
+    <t>预留：确认浏览器启动成功后允许领取</t>
+  </si>
+  <si>
+    <t>ELinkTreeRewardType</t>
+  </si>
+  <si>
+    <t>LinkTree 可领取奖励类型</t>
+  </si>
+  <si>
+    <t>无奖励</t>
+  </si>
+  <si>
+    <t>只记录访问/领取状态，不发实际奖励</t>
+  </si>
+  <si>
+    <t>FixedItem</t>
+  </si>
+  <si>
+    <t>固定道具</t>
+  </si>
+  <si>
+    <t>所有玩家领取相同的 RewardItemId 道具</t>
+  </si>
+  <si>
+    <t>FixedChips</t>
+  </si>
+  <si>
+    <t>固定筹码</t>
+  </si>
+  <si>
+    <t>所有玩家领取相同数量的 RewardChips 筹码</t>
+  </si>
+  <si>
+    <t>SequentialPack</t>
+  </si>
+  <si>
+    <t>顺序礼包</t>
+  </si>
+  <si>
+    <t>按玩家个人领取进度依次发放礼包格子；最后一格可重复兜底，当前预留</t>
+  </si>
+  <si>
     <t>ESteamItemDefType</t>
   </si>
   <si>
-    <t>Steam定义的物品类型</t>
+    <t>Steam物品定义类型</t>
   </si>
   <si>
     <t>Item</t>
   </si>
   <si>
-    <t>物品</t>
-  </si>
-  <si>
-    <t>这个显式枚举值可能会变，到时候会改成Steam要求的枚举值，因此使用时不要根据int值来判断</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>EAchievementRuleType</t>
-  </si>
-  <si>
-    <t>成就判定规则</t>
-  </si>
-  <si>
-    <t>FirstExternalItemType</t>
-  </si>
-  <si>
-    <t>首次获得非初始道具部位</t>
-  </si>
-  <si>
-    <t>FirstExternalItemRarity</t>
-  </si>
-  <si>
-    <t>首次获得非初始指定品质道具</t>
-  </si>
-  <si>
-    <t>FirstEvent</t>
-  </si>
-  <si>
-    <t>首次发生游戏事件</t>
-  </si>
-  <si>
-    <t>StatisticAtLeast</t>
-  </si>
-  <si>
-    <t>玩家统计达到数值</t>
-  </si>
-  <si>
-    <t>EPlayerStatisticUnit</t>
-  </si>
-  <si>
-    <t>玩家统计单位</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>次数</t>
-  </si>
-  <si>
-    <t>Chips</t>
-  </si>
-  <si>
-    <t>筹码</t>
-  </si>
-  <si>
-    <t>Seconds</t>
-  </si>
-  <si>
-    <t>秒</t>
-  </si>
-  <si>
-    <t>EPlayerStatisticType</t>
-  </si>
-  <si>
-    <t>玩家统计类型</t>
-  </si>
-  <si>
-    <t>Counter</t>
-  </si>
-  <si>
-    <t>只增累计</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>最高记录</t>
+    <t>普通物品</t>
+  </si>
+  <si>
+    <t>普通物品。可以实际存在于玩家 Steam 库存中的基础物品，例如装扮、盲盒、开箱券或永久领奖回执。</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>礼包</t>
+  </si>
+  <si>
+    <t>礼包。发放时会自动拆成预先配置的一组物品，适合一次发放多个固定奖励。</t>
+  </si>
+  <si>
+    <t>Generator</t>
+  </si>
+  <si>
+    <t>随机生成器</t>
+  </si>
+  <si>
+    <t>随机生成器。发放时会按配置的权重随机生成一种或多种结果物品；生成器本身不会留在玩家库存里。</t>
+  </si>
+  <si>
+    <t>PlaytimeGenerator</t>
+  </si>
+  <si>
+    <t>游玩投放生成器</t>
+  </si>
+  <si>
+    <t>游玩投放生成器。由游戏在合适时机请求投放，Steam 根据玩家游玩时间、冷却和次数限制决定是否发放随机奖励，适合定时盲盒掉落。</t>
+  </si>
+  <si>
+    <t>TagGenerator</t>
+  </si>
+  <si>
+    <t>标签生成器</t>
+  </si>
+  <si>
+    <t>标签生成器。发放物品时为该物品随机附加标签或词条，例如品质、颜色、稀有特性；当前项目暂时不需要。</t>
+  </si>
+  <si>
+    <t>EBlindBoxValueMode</t>
+  </si>
+  <si>
+    <t>盲盒气球提示的数量显示模式</t>
+  </si>
+  <si>
+    <t>显示消耗筹码数值</t>
+  </si>
+  <si>
+    <t>显示x1</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>显示本地化“免费”</t>
   </si>
 </sst>
 </file>
@@ -1769,7 +1901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -3071,189 +3203,277 @@
       </c>
     </row>
     <row r="92" spans="1:12">
+      <c r="A92" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="B92" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C92" s="5" t="b">
+        <v>222</v>
+      </c>
+      <c r="C92" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D92" s="5" t="b">
+      <c r="D92" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E92" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="F92" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J92" s="1">
         <v>1</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J93" s="1">
+        <v>2</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J94" s="1">
+        <v>3</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C95" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D95" s="1" t="b">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J95" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
+      </c>
+      <c r="C96" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J96" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J97" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J98" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C99" s="1" t="b">
         <v>0</v>
@@ -3262,180 +3482,449 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J99" s="1">
         <v>1</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J100" s="1">
         <v>2</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:12">
-      <c r="A101" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>246</v>
+      </c>
+      <c r="C101" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:12">
-      <c r="A102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="B102" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C102" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D102" s="1" t="b">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J102" s="1">
         <v>1</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:12">
-      <c r="A103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="B103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J103" s="1">
         <v>2</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>226</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="B104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J104" s="1">
+        <v>3</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="B105" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C105" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J105" s="1">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="B106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J106" s="1">
+        <v>1</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="B107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J107" s="1">
+        <v>2</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="B108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J108" s="1">
+        <v>3</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="B109" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C109" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="H110" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="J110" s="1">
+        <v>2</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="H111" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J111" s="1">
+        <v>3</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="H112" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="J112" s="1">
+        <v>4</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
+      <c r="H113" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
+      <c r="B114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C114" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11">
+      <c r="H115" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J115" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11">
+      <c r="H116" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J116" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak2/xlsx/__enums__.xlsx
+++ b/luban-excels/bak2/xlsx/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="298">
   <si>
     <t>##var</t>
   </si>
@@ -843,6 +843,15 @@
   </si>
   <si>
     <t>按玩家个人领取进度依次发放礼包格子；最后一格可重复兜底，当前预留</t>
+  </si>
+  <si>
+    <t>BlindBox</t>
+  </si>
+  <si>
+    <t>奖励盲盒</t>
+  </si>
+  <si>
+    <t>奖励玩家盲盒票并自动开启</t>
   </si>
   <si>
     <t>ESteamItemDefType</t>
@@ -1901,7 +1910,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -3801,32 +3810,32 @@
       </c>
     </row>
     <row r="109" spans="1:12">
-      <c r="B109" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C109" s="1" t="b">
+      <c r="I109" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J109" s="1">
+        <v>4</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="B110" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="b">
+      <c r="D110" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F109" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J109" s="1">
-        <v>1</v>
-      </c>
-      <c r="K109" s="5" t="s">
+      <c r="F110" s="1" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="110" spans="1:12">
       <c r="H110" s="5" t="s">
         <v>277</v>
       </c>
@@ -3834,7 +3843,7 @@
         <v>278</v>
       </c>
       <c r="J110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" s="5" t="s">
         <v>279</v>
@@ -3848,7 +3857,7 @@
         <v>281</v>
       </c>
       <c r="J111" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K111" s="5" t="s">
         <v>282</v>
@@ -3862,7 +3871,7 @@
         <v>284</v>
       </c>
       <c r="J112" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>285</v>
@@ -3876,54 +3885,68 @@
         <v>287</v>
       </c>
       <c r="J113" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="114" spans="2:11">
-      <c r="B114" s="1" t="s">
+      <c r="H114" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C114" s="1" t="b">
+      <c r="I114" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11">
+      <c r="B115" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="b">
+      <c r="D115" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="H114" s="1" t="s">
+      <c r="F115" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H115" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I114" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="J114" s="1">
+      <c r="I115" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J115" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11">
-      <c r="H115" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="J115" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="116" spans="2:11">
       <c r="H116" s="1" t="s">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J116" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11">
+      <c r="H117" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J117" s="1">
         <v>3</v>
       </c>
     </row>
